--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -3786,7 +3786,7 @@
         <v>136193896</v>
       </c>
       <c r="B31" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136193897</v>
       </c>
       <c r="B32" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -3786,7 +3786,7 @@
         <v>136193896</v>
       </c>
       <c r="B31" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136193897</v>
       </c>
       <c r="B32" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -3786,7 +3786,7 @@
         <v>136193896</v>
       </c>
       <c r="B31" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136193897</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 44198-2025 artfynd.xlsx
+++ b/artfynd/A 44198-2025 artfynd.xlsx
@@ -3786,7 +3786,7 @@
         <v>136193896</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136193897</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
